--- a/artfynd/A 10603-2023 artfynd.xlsx
+++ b/artfynd/A 10603-2023 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>103037</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Stare</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Sturnus vulgaris</t>
@@ -808,11 +803,6 @@
       </c>
       <c r="E3" t="n">
         <v>208255</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Skogsödla</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 10603-2023 artfynd.xlsx
+++ b/artfynd/A 10603-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122501166</v>
+        <v>122501168</v>
       </c>
       <c r="B2" t="n">
-        <v>57784</v>
+        <v>56342</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,26 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>208255</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563099</v>
+        <v>563215</v>
       </c>
       <c r="R2" t="n">
-        <v>6254253</v>
+        <v>6254354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122501168</v>
+        <v>122501166</v>
       </c>
       <c r="B3" t="n">
-        <v>56338</v>
+        <v>57788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,26 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>103037</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563215</v>
+        <v>563099</v>
       </c>
       <c r="R3" t="n">
-        <v>6254354</v>
+        <v>6254253</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10603-2023 artfynd.xlsx
+++ b/artfynd/A 10603-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122501168</v>
+        <v>122501166</v>
       </c>
       <c r="B2" t="n">
-        <v>56342</v>
+        <v>57788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208255</v>
+        <v>103037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563215</v>
+        <v>563099</v>
       </c>
       <c r="R2" t="n">
-        <v>6254354</v>
+        <v>6254253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122501166</v>
+        <v>122501168</v>
       </c>
       <c r="B3" t="n">
-        <v>57788</v>
+        <v>56342</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563099</v>
+        <v>563215</v>
       </c>
       <c r="R3" t="n">
-        <v>6254253</v>
+        <v>6254354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,11 +872,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10603-2023 artfynd.xlsx
+++ b/artfynd/A 10603-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122501166</v>
+        <v>122501168</v>
       </c>
       <c r="B2" t="n">
-        <v>57788</v>
+        <v>56342</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>208255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563099</v>
+        <v>563215</v>
       </c>
       <c r="R2" t="n">
-        <v>6254253</v>
+        <v>6254354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122501168</v>
+        <v>122501166</v>
       </c>
       <c r="B3" t="n">
-        <v>56342</v>
+        <v>57788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563215</v>
+        <v>563099</v>
       </c>
       <c r="R3" t="n">
-        <v>6254354</v>
+        <v>6254253</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10603-2023 artfynd.xlsx
+++ b/artfynd/A 10603-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122501168</v>
+        <v>122501166</v>
       </c>
       <c r="B2" t="n">
-        <v>56342</v>
+        <v>57789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208255</v>
+        <v>103037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563215</v>
+        <v>563099</v>
       </c>
       <c r="R2" t="n">
-        <v>6254354</v>
+        <v>6254253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122501166</v>
+        <v>122501168</v>
       </c>
       <c r="B3" t="n">
-        <v>57788</v>
+        <v>56343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563099</v>
+        <v>563215</v>
       </c>
       <c r="R3" t="n">
-        <v>6254253</v>
+        <v>6254354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,11 +872,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10603-2023 artfynd.xlsx
+++ b/artfynd/A 10603-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122501166</v>
+        <v>122501168</v>
       </c>
       <c r="B2" t="n">
-        <v>57789</v>
+        <v>56343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>208255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563099</v>
+        <v>563215</v>
       </c>
       <c r="R2" t="n">
-        <v>6254253</v>
+        <v>6254354</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122501168</v>
+        <v>122501166</v>
       </c>
       <c r="B3" t="n">
-        <v>56343</v>
+        <v>57789</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563215</v>
+        <v>563099</v>
       </c>
       <c r="R3" t="n">
-        <v>6254354</v>
+        <v>6254253</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10603-2023 artfynd.xlsx
+++ b/artfynd/A 10603-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122501168</v>
       </c>
       <c r="B2" t="n">
-        <v>56343</v>
+        <v>56437</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>122501166</v>
       </c>
       <c r="B3" t="n">
-        <v>57789</v>
+        <v>57883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 10603-2023 artfynd.xlsx
+++ b/artfynd/A 10603-2023 artfynd.xlsx
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122501168</v>
+        <v>122501166</v>
       </c>
       <c r="B2" t="n">
-        <v>56437</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208255</v>
+        <v>103037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563215</v>
+        <v>563099</v>
       </c>
       <c r="R2" t="n">
-        <v>6254354</v>
+        <v>6254253</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,43 +786,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122501166</v>
+        <v>122501168</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563099</v>
+        <v>563215</v>
       </c>
       <c r="R3" t="n">
-        <v>6254253</v>
+        <v>6254354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Starungar i hålträd</t>
         </is>
       </c>
       <c r="AD3" t="b">
